--- a/escalation_handover.xlsx
+++ b/escalation_handover.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,6 +639,74 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>14:25:54</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Returns &amp; Exchange</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>assistant: Hi, I'm an AI support assistant. I'll do my best to help you with your request. How may I help you today?
+user: how long does the return take 
+assistant: Return processing typically takes 7-10 business days after our warehouse receives the returned item. Once processed, your refund or exchange will be shipped out via your preferred method, which may take an additional 3-7 business days.
+Has your issue been resolved? Please reply Yes or No.
+user: No
+assistant: Could you describe your issue in more detail so we can better assist you?
+user: im angry , could you hurry up. 
+assistant: We have clearly understood and recorded your question and request. We will resolve your issue as quickly as possible. Our helpful and professional staff will contact you shortly. Thank you for your patience!</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>The customer's item return is taking longer than expected and they are requesting a faster resolution. They expressed frustration with the process and requested their issue be escalated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>14:33:28</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Returns &amp; Exchange</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>assistant: Hi, I'm an AI support assistant. I'll do my best to help you with your request. How may I help you today?
+user: how long does the return take
+assistant: Processing a return typically takes 5-10 business days from the date we receive the returned item. Once your return is processed, you will receive an email with a confirmation of the refund and the status of any exchange or replacement item.
+Has your issue been resolved? Please reply Yes or No.
+user: No
+assistant: Could you describe your issue in more detail so we can better assist you?
+user: im upset, you hurry up tell me
+assistant: We have clearly understood and recorded your question and request. We will resolve your issue as quickly as possible. Our helpful and professional staff will contact you shortly. Thank you for your patience!</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>A customer is attempting to return an item but is concerned about the processing time which is typically 5-10 business days. They are upset and frustrated with the current response, and our human escalation team will need to review the situation to provide a more empathetic and personalized solution. We need to address their concerns and provide a resolution in a timely manner to escalate their issue correctly.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/escalation_handover.xlsx
+++ b/escalation_handover.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,6 +707,40 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>14:37:14</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Returns &amp; Exchange</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>assistant: Hi, I'm an AI support assistant. I'll do my best to help you with your request. How may I help you today?
+user: how long dose the return take
+assistant: Our return process takes approximately 7-10 business days for processing once we receive the returned item. After that, the refund or replacement will be shipped out to you within the additional 3-5 business days, depending on your location.
+Has your issue been resolved? Please reply Yes or No.
+user: No
+assistant: Could you describe your issue in more detail so we can better assist you?
+user: im angry ,could you hurry up
+assistant: We have clearly understood and recorded your question and request. We will resolve your issue as quickly as possible. Our helpful and professional staff will contact you shortly. Thank you for your patience!</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>The customer has initiated a Returns &amp; Exchange ticket due to a delayed return process, and is requesting faster resolution. The current status is that returns take 7-10 business days for processing, followed by an additional 3-5 business days for the refund or replacement to be shipped. The customer has expressed frustration and urgency due to the delay.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
